--- a/output/xlsx/AdministradorEditaCompatibilidade--GT-.xlsx
+++ b/output/xlsx/AdministradorEditaCompatibilidade--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="61">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 9 test case(s)</t>
+    <t>Size: 8 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -122,7 +122,7 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Ordena lista de Compatibilidades</t>
+    <t>Alternative Flow 1: Usuario ordena lista de Compatibilidades</t>
   </si>
   <si>
     <t>Administrador: clica em um dos botões de ordenacao associada a uma coluna da tabela</t>
@@ -131,7 +131,7 @@
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Filtra lista de Compatibilidades</t>
+    <t>Alternative Flow 2: Usuario filtra lista de Compatibilidades</t>
   </si>
   <si>
     <t>Administrador: preenche campos de filtragem</t>
@@ -140,7 +140,7 @@
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Navega por paginas de tabela</t>
+    <t>Alternative Flow 3: Usuario navega por paginas de tabela</t>
   </si>
   <si>
     <t>Administrador: clica em botao de navegacao de paginas de tabela</t>
@@ -149,7 +149,7 @@
     <t>TC5</t>
   </si>
   <si>
-    <t>Alternative Flow 4: Cancela atualizacao de Compatibilidade</t>
+    <t>Alternative Flow 4: Usuario cancela atualizacao de Compatibilidade</t>
   </si>
   <si>
     <t>Administrador: clica no botao Cancelar</t>
@@ -158,43 +158,34 @@
     <t>TC6</t>
   </si>
   <si>
-    <t>Alternative Flow 5: Volta para tela inicial de sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao Voltar</t>
+    <t>Exception Flow 1: Nao insere algum dado obrigatorio'</t>
+  </si>
+  <si>
+    <t>SYSTEM informa que os dados obrigatorios devem ser preenchidos</t>
+  </si>
+  <si>
+    <t>Administrador: preenche dados obrigatorios e clica em Atualizar</t>
+  </si>
+  <si>
+    <t>SYSTEM processes action successfully</t>
+  </si>
+  <si>
+    <t>Flow interrupted due to exception / error</t>
   </si>
   <si>
     <t>TC7</t>
   </si>
   <si>
-    <t>Exception Flow 1: Nao insere algum dado obrigatorio'</t>
-  </si>
-  <si>
-    <t>SYSTEM informa que os dados obrigatorios devem ser preenchidos</t>
-  </si>
-  <si>
-    <t>Administrador: preenche dados obrigatorios e clica em Atualizar</t>
-  </si>
-  <si>
-    <t>SYSTEM processes action successfully</t>
-  </si>
-  <si>
-    <t>Flow interrupted due to exception / error</t>
+    <t>Exception Flow 2: Usuario insere Tipo de Mercadoria invalido</t>
+  </si>
+  <si>
+    <t>SYSTEM alerta que Horario de Inicio é invalido</t>
+  </si>
+  <si>
+    <t>Administrador: preenche um Tipo de Mercadoria valida e clica em Atualizar</t>
   </si>
   <si>
     <t>TC8</t>
-  </si>
-  <si>
-    <t>Exception Flow 2: Usuario insere Tipo de Mercadoria invalido</t>
-  </si>
-  <si>
-    <t>SYSTEM alerta que Horario de Inicio é invalido</t>
-  </si>
-  <si>
-    <t>Administrador: preenche um Tipo de Mercadoria valida e clica em Atualizar</t>
-  </si>
-  <si>
-    <t>TC9</t>
   </si>
   <si>
     <t>Exception Flow 3: Usuario insere NCM invalido</t>
@@ -295,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -1128,13 +1119,13 @@
         <v>2.0</v>
       </c>
       <c r="B66" t="s" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D66" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s" s="3">
         <v>27</v>
@@ -1148,13 +1139,13 @@
         <v>3.0</v>
       </c>
       <c r="B67" t="s" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D67" t="s" s="3">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E67" t="s" s="3">
         <v>27</v>
@@ -1168,13 +1159,13 @@
         <v>4.0</v>
       </c>
       <c r="B68" t="s" s="3">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D68" t="s" s="3">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s" s="3">
         <v>27</v>
@@ -1188,7 +1179,7 @@
         <v>33</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72">
@@ -1196,7 +1187,7 @@
         <v>11</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>13</v>
@@ -1210,7 +1201,7 @@
         <v>15</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E73" t="s" s="1">
         <v>17</v>
@@ -1295,7 +1286,7 @@
         <v>27</v>
       </c>
       <c r="D78" t="s" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E78" t="s" s="3">
         <v>27</v>
@@ -1309,13 +1300,13 @@
         <v>4.0</v>
       </c>
       <c r="B79" t="s" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C79" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D79" t="s" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E79" t="s" s="3">
         <v>27</v>
@@ -1329,7 +1320,7 @@
         <v>33</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83">
@@ -1337,7 +1328,7 @@
         <v>11</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>13</v>
@@ -1351,7 +1342,7 @@
         <v>15</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E84" t="s" s="1">
         <v>17</v>
@@ -1436,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="D89" t="s" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E89" t="s" s="3">
         <v>27</v>
@@ -1450,13 +1441,13 @@
         <v>4.0</v>
       </c>
       <c r="B90" t="s" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C90" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D90" t="s" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E90" t="s" s="3">
         <v>27</v>
@@ -1470,148 +1461,7 @@
         <v>33</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B94" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C94" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="E95" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B96" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B98" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C98" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D98" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E98" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F98" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B99" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C99" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D99" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E99" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F99" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B100" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C100" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D100" t="s" s="3">
-        <v>62</v>
-      </c>
-      <c r="E100" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F100" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B101" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="C101" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D101" t="s" s="3">
-        <v>54</v>
-      </c>
-      <c r="E101" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F101" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B102" t="s" s="0">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
